--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jai Mata Dii\DBS_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Ixigo_Automation 9\Ixigo_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8690" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Capabilities" sheetId="1" r:id="rId1"/>
@@ -18,22 +18,11 @@
     <sheet name="DeviceMasterSheet" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="91">
   <si>
     <t>ApplicationActivity</t>
   </si>
@@ -92,9 +81,6 @@
     <t>webkitDebugProxyPort</t>
   </si>
   <si>
-    <t>app</t>
-  </si>
-  <si>
     <t>Device</t>
   </si>
   <si>
@@ -113,12 +99,6 @@
     <t>Password</t>
   </si>
   <si>
-    <t>com.dbs.sg.digibank.ui.demo.SplashActivity</t>
-  </si>
-  <si>
-    <t>com.dbs.sit1.dbsmbanking</t>
-  </si>
-  <si>
     <t>Manafacturer</t>
   </si>
   <si>
@@ -128,31 +108,7 @@
     <t>Max_Ver</t>
   </si>
   <si>
-    <t>10.0.0</t>
-  </si>
-  <si>
     <t>Individual_ID</t>
-  </si>
-  <si>
-    <t>12.0.0</t>
-  </si>
-  <si>
-    <t>Xiaomi</t>
-  </si>
-  <si>
-    <t>121212</t>
-  </si>
-  <si>
-    <t>AppName</t>
-  </si>
-  <si>
-    <t>DBS</t>
-  </si>
-  <si>
-    <t>sakshi.juneja@crestechsoftware.com</t>
-  </si>
-  <si>
-    <t>t68k6kw68ywjv2y9zwfr9r3t</t>
   </si>
   <si>
     <t>S2021219EUID</t>
@@ -283,31 +239,79 @@
     <t>r36d4py9mtkykt29c925c7mg</t>
   </si>
   <si>
-    <t>dbs_android_UAT_7_10_003_532.apk</t>
-  </si>
-  <si>
-    <t>SGMB_ONEAPP_MB-12-3-42.ipa</t>
-  </si>
-  <si>
-    <t>SAMSUNG_GalaxyOnMax_Android_8.1.0_85564</t>
-  </si>
-  <si>
-    <t>MOTOROLA_MotoG5_Android_8.1.0_c3d6c</t>
-  </si>
-  <si>
-    <t>XIAOMI_Redmi6_Android_9.0.0_ed157</t>
-  </si>
-  <si>
-    <t>XIAOMI_RedmiNote7Pro_Android_9.0.0_059d9</t>
-  </si>
-  <si>
-    <t>XIAOMI_RedmiNote9_Android_10.0.0_a7454</t>
+    <t>EndPoint</t>
+  </si>
+  <si>
+    <t>https://device.pcloudy.com</t>
   </si>
   <si>
     <t>8.1.0</t>
   </si>
   <si>
-    <t>9.0.0</t>
+    <t>AppName</t>
+  </si>
+  <si>
+    <t>3672</t>
+  </si>
+  <si>
+    <t>com.ixigo.travel</t>
+  </si>
+  <si>
+    <t>ixigo_Resigned1732623468.ipa</t>
+  </si>
+  <si>
+    <t>15.0.0</t>
+  </si>
+  <si>
+    <t>SAMSUNG_GalaxyS215G_Android_14.0.0_5ba8b</t>
+  </si>
+  <si>
+    <t>SAMSUNG_GalaxyF145G_Android_13.0.0_dd226</t>
+  </si>
+  <si>
+    <t>https://ind-west.pcloudy.com</t>
+  </si>
+  <si>
+    <t>GOOGLE_Pixel9_Android_15.0.0_06a75</t>
+  </si>
+  <si>
+    <t>GOOGLE_Pixel4_Android_12.0.0_4b678</t>
+  </si>
+  <si>
+    <t>APPLE_iPhone11ProMax_iOS_15.0.0_b99a8</t>
+  </si>
+  <si>
+    <t>7701833994</t>
+  </si>
+  <si>
+    <t>shyam.dheer@crestechsoftware.com</t>
+  </si>
+  <si>
+    <t>mj2dswjphhw8b254tx8j2kkj</t>
+  </si>
+  <si>
+    <t>eu.afse.omnia.mcb.curacao</t>
+  </si>
+  <si>
+    <t>eu.afse.omnia.prototype.usecases.splash.SplashScreenActivity</t>
+  </si>
+  <si>
+    <t>https://private-poc.pcloudy.com</t>
+  </si>
+  <si>
+    <t>MCB.apk</t>
+  </si>
+  <si>
+    <t>SAMSUNG_GalaxyA33_Android_14.0.0_2944d</t>
+  </si>
+  <si>
+    <t>14.0.0</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>MCB</t>
   </si>
 </sst>
 </file>
@@ -371,7 +375,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -381,32 +385,41 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -414,9 +427,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -435,9 +447,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -445,9 +454,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -456,17 +462,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -774,401 +802,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.28515625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="48.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="37" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="63.5703125" style="4" customWidth="1"/>
-    <col min="16" max="16" width="26.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="14.7109375" style="4"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.36328125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="48.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="37" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="63.54296875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="26.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="14.6328125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="H3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="6" t="s">
+      <c r="K3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="L3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>22</v>
+      <c r="M3" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1"/>
+    <hyperlink ref="D2" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="17.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="40.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="11">
+      <c r="B9" s="16">
         <v>1</v>
       </c>
-      <c r="C9" s="11">
-        <v>2</v>
-      </c>
-      <c r="D9" s="11">
-        <v>3</v>
-      </c>
-      <c r="E9" s="11">
-        <v>4</v>
-      </c>
-      <c r="F9" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-    </row>
-    <row r="13" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="45" orientation="portrait" r:id="rId1"/>
@@ -1177,32 +1080,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.6328125" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B1">
         <v>1</v>
       </c>
@@ -1264,165 +1167,165 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>60</v>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" t="s">
         <v>40</v>
       </c>
-      <c r="D2" t="s">
+      <c r="N2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" t="s">
+      <c r="O2" t="s">
         <v>42</v>
       </c>
-      <c r="F2" t="s">
+      <c r="P2" t="s">
         <v>43</v>
       </c>
-      <c r="G2" t="s">
+      <c r="Q2" t="s">
         <v>44</v>
       </c>
-      <c r="H2" t="s">
+      <c r="R2" t="s">
         <v>45</v>
       </c>
-      <c r="I2" t="s">
+      <c r="S2" t="s">
         <v>46</v>
       </c>
-      <c r="J2" t="s">
+      <c r="T2" t="s">
         <v>47</v>
       </c>
-      <c r="K2" t="s">
+      <c r="U2" t="s">
         <v>48</v>
       </c>
-      <c r="L2" t="s">
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3" s="20"/>
+      <c r="B3">
+        <v>121212</v>
+      </c>
+      <c r="C3">
+        <v>121212</v>
+      </c>
+      <c r="D3">
+        <v>121212</v>
+      </c>
+      <c r="E3">
+        <v>121212</v>
+      </c>
+      <c r="F3">
+        <v>121212</v>
+      </c>
+      <c r="G3">
+        <v>121212</v>
+      </c>
+      <c r="H3">
+        <v>121212</v>
+      </c>
+      <c r="I3">
+        <v>121212</v>
+      </c>
+      <c r="J3">
+        <v>121212</v>
+      </c>
+      <c r="K3">
+        <v>121212</v>
+      </c>
+      <c r="L3">
+        <v>121212</v>
+      </c>
+      <c r="M3">
+        <v>121212</v>
+      </c>
+      <c r="N3">
+        <v>121212</v>
+      </c>
+      <c r="O3">
+        <v>121212</v>
+      </c>
+      <c r="P3">
+        <v>121212</v>
+      </c>
+      <c r="Q3">
+        <v>121212</v>
+      </c>
+      <c r="R3">
+        <v>121212</v>
+      </c>
+      <c r="S3">
+        <v>121212</v>
+      </c>
+      <c r="T3">
+        <v>121212</v>
+      </c>
+      <c r="U3">
+        <v>121212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="M2" t="s">
+    </row>
+    <row r="5" spans="1:21" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="N2" t="s">
+    </row>
+    <row r="7" spans="1:21" ht="116" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="O2" t="s">
+    </row>
+    <row r="8" spans="1:21" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="P2" t="s">
+    </row>
+    <row r="9" spans="1:21" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="Q2" t="s">
-        <v>55</v>
-      </c>
-      <c r="R2" t="s">
-        <v>56</v>
-      </c>
-      <c r="S2" t="s">
-        <v>57</v>
-      </c>
-      <c r="T2" t="s">
-        <v>58</v>
-      </c>
-      <c r="U2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="15"/>
-      <c r="B3">
-        <v>121212</v>
-      </c>
-      <c r="C3">
-        <v>121212</v>
-      </c>
-      <c r="D3">
-        <v>121212</v>
-      </c>
-      <c r="E3">
-        <v>121212</v>
-      </c>
-      <c r="F3">
-        <v>121212</v>
-      </c>
-      <c r="G3">
-        <v>121212</v>
-      </c>
-      <c r="H3">
-        <v>121212</v>
-      </c>
-      <c r="I3">
-        <v>121212</v>
-      </c>
-      <c r="J3">
-        <v>121212</v>
-      </c>
-      <c r="K3">
-        <v>121212</v>
-      </c>
-      <c r="L3">
-        <v>121212</v>
-      </c>
-      <c r="M3">
-        <v>121212</v>
-      </c>
-      <c r="N3">
-        <v>121212</v>
-      </c>
-      <c r="O3">
-        <v>121212</v>
-      </c>
-      <c r="P3">
-        <v>121212</v>
-      </c>
-      <c r="Q3">
-        <v>121212</v>
-      </c>
-      <c r="R3">
-        <v>121212</v>
-      </c>
-      <c r="S3">
-        <v>121212</v>
-      </c>
-      <c r="T3">
-        <v>121212</v>
-      </c>
-      <c r="U3">
-        <v>121212</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="120" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>1</v>
       </c>
@@ -1445,34 +1348,34 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>67</v>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A12" s="21" t="s">
+        <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A13" s="21"/>
       <c r="B13">
         <v>121212</v>
       </c>
@@ -1495,60 +1398,34 @@
         <v>121212</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="75" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="120" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:1" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="18" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="18" t="s">
-        <v>83</v>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="58" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="116" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1563,9 +1440,235 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:B64"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="53.90625" customWidth="1"/>
+    <col min="2" max="2" width="25.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="23"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="20"/>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="12"/>
+    </row>
+    <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="12"/>
+    </row>
+    <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="12"/>
+    </row>
+    <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="12"/>
+    </row>
+    <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="12"/>
+    </row>
+    <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="12"/>
+    </row>
+    <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="12"/>
+    </row>
+    <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="12"/>
+    </row>
+    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="12"/>
+    </row>
+    <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="12"/>
+    </row>
+    <row r="16" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="12"/>
+    </row>
+    <row r="17" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="12"/>
+    </row>
+    <row r="18" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="12"/>
+    </row>
+    <row r="19" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="12"/>
+    </row>
+    <row r="20" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="12"/>
+    </row>
+    <row r="21" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="12"/>
+    </row>
+    <row r="22" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="12"/>
+    </row>
+    <row r="23" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="12"/>
+    </row>
+    <row r="24" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="12"/>
+    </row>
+    <row r="25" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="12"/>
+    </row>
+    <row r="26" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="12"/>
+    </row>
+    <row r="27" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="12"/>
+    </row>
+    <row r="28" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="12"/>
+    </row>
+    <row r="29" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="12"/>
+    </row>
+    <row r="30" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="12"/>
+    </row>
+    <row r="31" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="12"/>
+    </row>
+    <row r="32" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="12"/>
+    </row>
+    <row r="33" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="12"/>
+    </row>
+    <row r="34" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="12"/>
+    </row>
+    <row r="35" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="12"/>
+    </row>
+    <row r="36" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="12"/>
+    </row>
+    <row r="37" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="12"/>
+    </row>
+    <row r="38" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="12"/>
+    </row>
+    <row r="39" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="12"/>
+    </row>
+    <row r="40" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="12"/>
+    </row>
+    <row r="41" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="12"/>
+    </row>
+    <row r="42" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="12"/>
+    </row>
+    <row r="43" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="12"/>
+    </row>
+    <row r="44" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="12"/>
+    </row>
+    <row r="45" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="12"/>
+    </row>
+    <row r="46" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="12"/>
+    </row>
+    <row r="47" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="12"/>
+    </row>
+    <row r="48" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="12"/>
+    </row>
+    <row r="49" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="12"/>
+    </row>
+    <row r="50" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="12"/>
+    </row>
+    <row r="51" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="12"/>
+    </row>
+    <row r="52" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="12"/>
+    </row>
+    <row r="53" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="12"/>
+    </row>
+    <row r="54" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="12"/>
+    </row>
+    <row r="55" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="12"/>
+    </row>
+    <row r="56" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="12"/>
+    </row>
+    <row r="57" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="12"/>
+    </row>
+    <row r="58" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="12"/>
+    </row>
+    <row r="59" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="12"/>
+    </row>
+    <row r="60" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="12"/>
+    </row>
+    <row r="61" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="12"/>
+    </row>
+    <row r="62" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="12"/>
+    </row>
+    <row r="63" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="12"/>
+    </row>
+    <row r="64" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="B3:B4"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>